--- a/data/trans_orig/Q5410-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5410-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2007</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59784</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87476</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89493</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65478</t>
+          <t>64610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70959</t>
+          <t>70935</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85238</t>
+          <t>85910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>94237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>248341</t>
+          <t>248918</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>257526</t>
+          <t>257528</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77553</t>
+          <t>77535</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84867</t>
+          <t>84868</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>330938</t>
+          <t>329806</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>341905</t>
+          <t>341845</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53696</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55465</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86697</t>
+          <t>86426</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96250</t>
+          <t>95125</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>142167</t>
+          <t>140975</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150609</t>
+          <t>150603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21344</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21735</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>397789</t>
+          <t>399067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>416051</t>
+          <t>416517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>401951</t>
+          <t>402154</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>420426</t>
+          <t>420529</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15451</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>38237</t>
+          <t>37608</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>487280</t>
+          <t>487055</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>497261</t>
+          <t>497958</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>641032</t>
+          <t>640852</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>661291</t>
+          <t>661170</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1132564</t>
+          <t>1132009</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1156679</t>
+          <t>1156276</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2012</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23198</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,47 +4743,47 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4680</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4778</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52499</t>
+          <t>51666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>59617</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,49 +4856,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17789</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14222</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18902</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>75,24%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17789</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14124</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18902</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>74,72%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>64</t>
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69125</t>
+          <t>68854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78406</t>
+          <t>78425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109584</t>
+          <t>110297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117704</t>
+          <t>117698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48279</t>
+          <t>48809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163538</t>
+          <t>163337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172262</t>
+          <t>172268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>19090</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23085</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>207259</t>
+          <t>207857</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225257</t>
+          <t>224225</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52794</t>
+          <t>53578</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>265351</t>
+          <t>264563</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282956</t>
+          <t>283206</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92122</t>
+          <t>92290</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101639</t>
+          <t>101544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163846</t>
+          <t>163957</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>180003</t>
+          <t>179627</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>261835</t>
+          <t>261166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>279200</t>
+          <t>279097</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23773</t>
+          <t>24617</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>362344</t>
+          <t>361596</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>381593</t>
+          <t>381848</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>364466</t>
+          <t>364915</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>383712</t>
+          <t>384067</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32180</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>17829</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40689</t>
+          <t>39184</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29010</t>
+          <t>30164</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32258</t>
+          <t>30318</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>27068</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51566</t>
+          <t>52922</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>522180</t>
+          <t>524191</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>543702</t>
+          <t>544707</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>683568</t>
+          <t>686246</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>711925</t>
+          <t>712560</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1218649</t>
+          <t>1218264</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1251199</t>
+          <t>1250665</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2016</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68647</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>99109</t>
+          <t>98647</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47407</t>
+          <t>47274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17588</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63802</t>
+          <t>64173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111754</t>
+          <t>110849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119461</t>
+          <t>119482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43887</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46209</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,42 +8773,42 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>163533</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>158103</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>165686</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>94,97%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>163533</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>158032</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>165692</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10016</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191685</t>
+          <t>190921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>200595</t>
+          <t>200586</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92007</t>
+          <t>92149</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>286482</t>
+          <t>286606</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>298565</t>
+          <t>298584</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133271</t>
+          <t>133198</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>142544</t>
+          <t>142728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149184</t>
+          <t>149934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158573</t>
+          <t>158584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>287677</t>
+          <t>287715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300050</t>
+          <t>299986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>385280</t>
+          <t>386111</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>403766</t>
+          <t>404355</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>385280</t>
+          <t>386111</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>403766</t>
+          <t>404355</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19363</t>
+          <t>18246</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25304</t>
+          <t>26510</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24019</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>564430</t>
+          <t>565250</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>580273</t>
+          <t>580081</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>735313</t>
+          <t>736697</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>757508</t>
+          <t>757047</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1306959</t>
+          <t>1306826</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1334096</t>
+          <t>1334721</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2023</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104941</t>
+          <t>104536</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62288</t>
+          <t>62492</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168252</t>
+          <t>168842</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138964</t>
+          <t>138759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93227</t>
+          <t>93816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100146</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49572</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52433</t>
+          <t>52428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145233</t>
+          <t>144970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152134</t>
+          <t>152072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11088</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>228728</t>
+          <t>228060</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>235523</t>
+          <t>235489</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>312940</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>326440</t>
+          <t>326358</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>548353</t>
+          <t>548211</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>562715</t>
+          <t>562323</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>527</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13695</t>
+          <t>14029</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16528</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85170</t>
+          <t>85090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90515</t>
+          <t>90544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186693</t>
+          <t>185930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>196231</t>
+          <t>195922</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>274585</t>
+          <t>273831</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>285160</t>
+          <t>285091</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>12756</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>11863</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23341</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23867</t>
+          <t>24288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>289800</t>
+          <t>289972</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>303849</t>
+          <t>304271</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>292991</t>
+          <t>291337</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>307366</t>
+          <t>307180</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20114</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22550</t>
+          <t>21709</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>43830</t>
+          <t>42880</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54136</t>
+          <t>53306</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>616837</t>
+          <t>617030</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>628524</t>
+          <t>628271</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>958684</t>
+          <t>960044</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>996562</t>
+          <t>995874</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1584936</t>
+          <t>1585519</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1618841</t>
+          <t>1619446</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5410-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5410-Clase-trans_orig.xlsx
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64610</t>
+          <t>64410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70935</t>
+          <t>70949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85910</t>
+          <t>85118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94237</t>
+          <t>94222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>248918</t>
+          <t>249195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>257528</t>
+          <t>258153</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77535</t>
+          <t>77473</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84868</t>
+          <t>84859</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>329806</t>
+          <t>331618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>341845</t>
+          <t>341937</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86426</t>
+          <t>86390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95125</t>
+          <t>95128</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>140975</t>
+          <t>141939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150603</t>
+          <t>150611</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21568</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21735</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>399067</t>
+          <t>399463</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>416517</t>
+          <t>417097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>402154</t>
+          <t>403522</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>420529</t>
+          <t>420952</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14884</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13950</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37608</t>
+          <t>36476</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>487055</t>
+          <t>487542</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>497958</t>
+          <t>497224</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>640852</t>
+          <t>639905</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>661170</t>
+          <t>661311</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1132009</t>
+          <t>1132945</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1156276</t>
+          <t>1156031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51666</t>
+          <t>51587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59617</t>
+          <t>59655</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14222</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68854</t>
+          <t>69272</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78425</t>
+          <t>78411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110297</t>
+          <t>108904</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117698</t>
+          <t>117696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48809</t>
+          <t>49622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163337</t>
+          <t>163381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172268</t>
+          <t>172280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>207857</t>
+          <t>206744</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>224225</t>
+          <t>224249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53578</t>
+          <t>53615</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>264563</t>
+          <t>265506</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>283206</t>
+          <t>283113</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>19739</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92290</t>
+          <t>92066</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101544</t>
+          <t>101612</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163957</t>
+          <t>164253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>179627</t>
+          <t>179975</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>261166</t>
+          <t>261589</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>279097</t>
+          <t>279381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24617</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>361596</t>
+          <t>360291</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>381848</t>
+          <t>381059</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>364915</t>
+          <t>362738</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>384067</t>
+          <t>383046</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12168</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>31430</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>19066</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39184</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>26221</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52922</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>524191</t>
+          <t>522665</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>544707</t>
+          <t>543920</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>686246</t>
+          <t>686238</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>712560</t>
+          <t>713206</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1218264</t>
+          <t>1217214</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1250665</t>
+          <t>1250171</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98647</t>
+          <t>98489</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47274</t>
+          <t>47153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>64250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110849</t>
+          <t>111550</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119482</t>
+          <t>119467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158103</t>
+          <t>158632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165686</t>
+          <t>165681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>190921</t>
+          <t>191475</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>200586</t>
+          <t>200583</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92149</t>
+          <t>91843</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>286606</t>
+          <t>286628</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>298584</t>
+          <t>298452</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13434</t>
+          <t>12170</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133198</t>
+          <t>133180</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>142728</t>
+          <t>142596</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149934</t>
+          <t>149176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158584</t>
+          <t>158579</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>287715</t>
+          <t>287616</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>299986</t>
+          <t>299972</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>16887</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>16887</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16636</t>
+          <t>15679</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16636</t>
+          <t>15679</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>386111</t>
+          <t>386297</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>404355</t>
+          <t>405025</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>386111</t>
+          <t>386297</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>404355</t>
+          <t>405025</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18246</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26510</t>
+          <t>24769</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>23743</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>565250</t>
+          <t>563887</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>580081</t>
+          <t>580085</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>736697</t>
+          <t>736248</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>757047</t>
+          <t>758139</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1306826</t>
+          <t>1307459</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1334721</t>
+          <t>1333713</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>663</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>639</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -11232,27 +11232,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106964</t>
+          <t>119738</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104536</t>
+          <t>116592</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11267,27 +11267,27 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64796</t>
+          <t>73920</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62492</t>
+          <t>70518</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11302,27 +11302,27 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>171759</t>
+          <t>193658</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168842</t>
+          <t>190943</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -11723,27 +11723,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>54733</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>52319</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -11758,17 +11758,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>141350</t>
+          <t>159448</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138759</t>
+          <t>156774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9566</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -12144,17 +12144,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>97715</t>
+          <t>107667</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93816</t>
+          <t>102898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>110392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51552</t>
+          <t>56672</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>54440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52428</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>149267</t>
+          <t>164339</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144970</t>
+          <t>159294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152072</t>
+          <t>167494</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>840</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12384,12 +12384,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>928</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12419,12 +12419,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -12487,17 +12487,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11088</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>232872</t>
+          <t>254313</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>228060</t>
+          <t>248279</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>235489</t>
+          <t>257115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>322584</t>
+          <t>126425</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>312940</t>
+          <t>122415</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>326358</t>
+          <t>128486</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>555456</t>
+          <t>380738</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>548211</t>
+          <t>374898</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>562323</t>
+          <t>384864</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,62 +12865,62 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>5552</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>0,95%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>5414</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>3139</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>9226</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12943,102 +12943,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>516</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>9855</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>16094</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>12078</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>7497</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>18196</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>5427</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>14029</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>10966</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>7114</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>16225</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>88447</t>
+          <t>97196</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85090</t>
+          <t>93631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90544</t>
+          <t>99382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,27 +13091,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>191816</t>
+          <t>205607</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185930</t>
+          <t>199320</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195922</t>
+          <t>210291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>280263</t>
+          <t>302804</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>273831</t>
+          <t>295706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>285091</t>
+          <t>308238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>204636</t>
+          <t>219640</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204636</t>
+          <t>219640</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>204636</t>
+          <t>219640</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>296642</t>
+          <t>320434</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296642</t>
+          <t>320434</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296642</t>
+          <t>320434</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12756</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12929</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>663</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>25919</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24288</t>
+          <t>26860</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -13512,27 +13512,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>297847</t>
+          <t>318964</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>289972</t>
+          <t>309587</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>304271</t>
+          <t>327163</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>300449</t>
+          <t>321577</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>291337</t>
+          <t>311700</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>307180</t>
+          <t>328680</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>22043</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>31438</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17636</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42880</t>
+          <t>43569</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>42553</t>
+          <t>46875</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27681</t>
+          <t>37557</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53306</t>
+          <t>58603</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>623598</t>
+          <t>686243</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>617030</t>
+          <t>679353</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>628271</t>
+          <t>691674</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>974946</t>
+          <t>836321</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>960044</t>
+          <t>824906</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>995874</t>
+          <t>845779</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1598544</t>
+          <t>1522564</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1585519</t>
+          <t>1509075</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1619446</t>
+          <t>1534298</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>637448</t>
+          <t>701010</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>637448</t>
+          <t>701010</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>637448</t>
+          <t>701010</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1018042</t>
+          <t>884218</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1018042</t>
+          <t>884218</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1018042</t>
+          <t>884218</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1655490</t>
+          <t>1585228</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1655490</t>
+          <t>1585228</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1655490</t>
+          <t>1585228</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
